--- a/data/trans_dic/P2C_R2-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P2C_R2-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados y estos son no remunerados</t>
+          <t>Hogares con al menos un miembro que requiere cuidados y estos son no remunerados (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>19,11; 24,14</t>
+          <t>19,29; 24,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>36,59; 43,12</t>
+          <t>36,33; 42,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25,03; 31,31</t>
+          <t>24,81; 31,08</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14,84; 20,78</t>
+          <t>14,64; 20,55</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>24,28; 29,13</t>
+          <t>24,08; 29,12</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,57; 46,27</t>
+          <t>40,4; 45,99</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,97; 36,96</t>
+          <t>30,82; 37,13</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>23,85; 28,34</t>
+          <t>23,66; 28,57</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>22,52; 25,96</t>
+          <t>22,58; 26,17</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39,7; 43,92</t>
+          <t>39,71; 44,1</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28,97; 33,61</t>
+          <t>29,08; 33,61</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>20,7; 24,48</t>
+          <t>20,87; 24,62</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>31,13; 35,81</t>
+          <t>31,15; 35,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>45,89; 50,37</t>
+          <t>45,92; 50,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30,66; 34,74</t>
+          <t>30,83; 34,8</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,99; 13,21</t>
+          <t>7,51; 13,08</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>37,93; 42,92</t>
+          <t>37,72; 42,81</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>55,51; 60,32</t>
+          <t>55,72; 60,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,44; 42,9</t>
+          <t>38,76; 43,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>14,93; 44,48</t>
+          <t>15,11; 42,38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>35,08; 38,47</t>
+          <t>35,16; 38,35</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>51,3; 54,55</t>
+          <t>51,24; 54,69</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>35,26; 38,2</t>
+          <t>35,04; 38,29</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,66; 30,18</t>
+          <t>12,56; 30,67</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>26,24; 34,26</t>
+          <t>26,23; 34,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>35,88; 45,54</t>
+          <t>35,97; 45,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>26,66; 35,05</t>
+          <t>27,17; 35,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,85; 13,37</t>
+          <t>7,95; 13,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>33,42; 42,42</t>
+          <t>33,06; 42,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>46,22; 56,45</t>
+          <t>46,64; 56,24</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>36,76; 44,8</t>
+          <t>36,48; 45,04</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,08; 13,22</t>
+          <t>9,3; 13,2</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>30,68; 36,8</t>
+          <t>30,57; 36,63</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>42,09; 49,11</t>
+          <t>42,2; 49,31</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>33,09; 38,87</t>
+          <t>32,48; 38,83</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,13; 12,6</t>
+          <t>9,12; 12,67</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>27,44; 30,83</t>
+          <t>27,54; 30,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>42,94; 46,7</t>
+          <t>43,04; 46,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29,73; 32,96</t>
+          <t>29,63; 32,98</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,29; 13,42</t>
+          <t>9,1; 13,44</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>32,87; 36,05</t>
+          <t>32,93; 36,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,94; 53,3</t>
+          <t>49,71; 53,16</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,13; 40,53</t>
+          <t>37,13; 40,64</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16,58; 37,05</t>
+          <t>16,62; 36,09</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>30,68; 32,91</t>
+          <t>30,84; 33,13</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>46,99; 49,39</t>
+          <t>46,93; 49,41</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>34,05; 36,39</t>
+          <t>33,96; 36,32</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,03; 25,99</t>
+          <t>14,02; 25,43</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados y estos son no remunerados</t>
+          <t>Hogares con al menos un miembro que requiere cuidados y estos son no remunerados (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>197199; 249049</t>
+          <t>199001; 250692</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>356617; 420238</t>
+          <t>354101; 416326</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>188811; 236198</t>
+          <t>187175; 234468</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>76399; 107019</t>
+          <t>75401; 105832</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>319343; 383110</t>
+          <t>316617; 382927</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>542731; 618945</t>
+          <t>540498; 615255</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>308008; 367595</t>
+          <t>306511; 369351</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>180178; 214080</t>
+          <t>178755; 215870</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>528403; 609244</t>
+          <t>530000; 614085</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>918087; 1015536</t>
+          <t>918371; 1019677</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>506726; 587853</t>
+          <t>508664; 587789</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>263002; 310958</t>
+          <t>265133; 312765</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>527150; 606385</t>
+          <t>527451; 605538</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>901167; 989244</t>
+          <t>901906; 990419</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>636539; 721259</t>
+          <t>640077; 722617</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>183098; 302500</t>
+          <t>171996; 299532</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>602168; 681407</t>
+          <t>598865; 679650</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>975761; 1060277</t>
+          <t>979400; 1065501</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>764354; 853021</t>
+          <t>770649; 854981</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>334101; 995450</t>
+          <t>338104; 948365</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1151134; 1262365</t>
+          <t>1153496; 1258175</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1909315; 2030316</t>
+          <t>1907119; 2035298</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1433012; 1552597</t>
+          <t>1424440; 1556375</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>573269; 1366589</t>
+          <t>568671; 1388735</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>144712; 188940</t>
+          <t>144627; 188324</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>172668; 219146</t>
+          <t>173084; 218433</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>145804; 191698</t>
+          <t>148610; 192795</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>50749; 86480</t>
+          <t>51391; 88319</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>159195; 202074</t>
+          <t>157496; 200591</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>211986; 258900</t>
+          <t>213919; 257928</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>201861; 246018</t>
+          <t>200332; 247330</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>59984; 87341</t>
+          <t>61398; 87154</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>315354; 378215</t>
+          <t>314220; 376466</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>395531; 461576</t>
+          <t>396623; 463409</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>362675; 426007</t>
+          <t>356025; 425595</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>119396; 164665</t>
+          <t>119173; 165568</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>899229; 1010203</t>
+          <t>902370; 1007998</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1468580; 1596940</t>
+          <t>1471706; 1590298</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1004295; 1113235</t>
+          <t>1000723; 1113981</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>320520; 463371</t>
+          <t>313974; 463942</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1110807; 1218215</t>
+          <t>1112673; 1224850</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1774871; 1894574</t>
+          <t>1766895; 1889323</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1311423; 1431695</t>
+          <t>1311616; 1435478</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>605770; 1353599</t>
+          <t>607145; 1318773</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2042280; 2190236</t>
+          <t>2052399; 2205057</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3277086; 3444669</t>
+          <t>3272612; 3446041</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2352996; 2514661</t>
+          <t>2346461; 2509717</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>996739; 1846447</t>
+          <t>996081; 1806787</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2C_R2-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P2C_R2-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,71%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>19,29; 24,3</t>
+          <t>19,15; 24,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>36,33; 42,72</t>
+          <t>36,52; 42,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24,81; 31,08</t>
+          <t>24,45; 30,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14,64; 20,55</t>
+          <t>14,82; 20,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>24,08; 29,12</t>
+          <t>23,9; 28,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,4; 45,99</t>
+          <t>40,44; 46,04</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,82; 37,13</t>
+          <t>30,71; 36,94</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>23,66; 28,57</t>
+          <t>24,37; 29,32</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>22,58; 26,17</t>
+          <t>22,56; 26,42</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39,71; 44,1</t>
+          <t>39,72; 43,81</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29,08; 33,61</t>
+          <t>28,63; 33,43</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>20,87; 24,62</t>
+          <t>20,93; 24,44</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>15,23%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>31,15; 35,76</t>
+          <t>30,91; 35,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>45,92; 50,43</t>
+          <t>45,8; 50,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30,83; 34,8</t>
+          <t>30,61; 34,83</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,51; 13,08</t>
+          <t>11,92; 15,29</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>37,72; 42,81</t>
+          <t>37,96; 42,76</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>55,72; 60,62</t>
+          <t>55,4; 60,31</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,76; 43,0</t>
+          <t>38,75; 43,11</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>15,11; 42,38</t>
+          <t>15,57; 18,66</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>35,16; 38,35</t>
+          <t>35,05; 38,48</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>51,24; 54,69</t>
+          <t>51,23; 54,51</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>35,04; 38,29</t>
+          <t>35,09; 38,24</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,56; 30,67</t>
+          <t>14,22; 16,4</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>11,25%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>26,23; 34,15</t>
+          <t>26,09; 34,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>35,97; 45,4</t>
+          <t>35,99; 45,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27,17; 35,25</t>
+          <t>26,7; 34,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,95; 13,66</t>
+          <t>8,33; 13,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>33,06; 42,1</t>
+          <t>33,21; 41,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>46,64; 56,24</t>
+          <t>46,18; 56,18</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>36,48; 45,04</t>
+          <t>36,4; 45,05</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,3; 13,2</t>
+          <t>9,54; 13,81</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>30,57; 36,63</t>
+          <t>30,53; 36,53</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>42,2; 49,31</t>
+          <t>42,16; 49,67</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>32,48; 38,83</t>
+          <t>32,67; 38,61</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,12; 12,67</t>
+          <t>9,6; 13,19</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>15,88%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>27,54; 30,76</t>
+          <t>27,69; 30,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>43,04; 46,5</t>
+          <t>43,06; 46,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29,63; 32,98</t>
+          <t>29,74; 32,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,1; 13,44</t>
+          <t>12,31; 14,9</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>32,93; 36,25</t>
+          <t>32,84; 36,14</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,71; 53,16</t>
+          <t>49,88; 53,35</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,13; 40,64</t>
+          <t>37,22; 40,71</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16,62; 36,09</t>
+          <t>16,94; 19,24</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>30,84; 33,13</t>
+          <t>30,74; 33,06</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>46,93; 49,41</t>
+          <t>47,0; 49,46</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>33,96; 36,32</t>
+          <t>34,11; 36,33</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,02; 25,43</t>
+          <t>15,06; 16,68</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>90034</t>
+          <t>99437</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>196162</t>
+          <t>218637</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>286196</t>
+          <t>318074</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>199001; 250692</t>
+          <t>197578; 248121</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>354101; 416326</t>
+          <t>355971; 418501</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>187175; 234468</t>
+          <t>184416; 233363</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>75401; 105832</t>
+          <t>85744; 116510</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>316617; 382927</t>
+          <t>314268; 379404</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>540498; 615255</t>
+          <t>540949; 615919</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>306511; 369351</t>
+          <t>305478; 367423</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>178755; 215870</t>
+          <t>200354; 241058</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>530000; 614085</t>
+          <t>529353; 620064</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>918371; 1019677</t>
+          <t>918445; 1013027</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>508664; 587789</t>
+          <t>500680; 584680</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>265133; 312765</t>
+          <t>293186; 342291</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>254803</t>
+          <t>301773</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>523245</t>
+          <t>368474</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>778048</t>
+          <t>670247</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>527451; 605538</t>
+          <t>523500; 603562</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>901906; 990419</t>
+          <t>899479; 990102</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>640077; 722617</t>
+          <t>635546; 723189</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>171996; 299532</t>
+          <t>265890; 341014</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>598865; 679650</t>
+          <t>602656; 678817</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>979400; 1065501</t>
+          <t>973783; 1060107</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>770649; 854981</t>
+          <t>770486; 857112</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>338104; 948365</t>
+          <t>338035; 405213</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1153496; 1258175</t>
+          <t>1150086; 1262413</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1907119; 2035298</t>
+          <t>1906649; 2028879</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1424440; 1556375</t>
+          <t>1426246; 1554209</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>568671; 1388735</t>
+          <t>626072; 721904</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>67394</t>
+          <t>76797</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>73295</t>
+          <t>85974</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>140689</t>
+          <t>162771</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>144627; 188324</t>
+          <t>143870; 190144</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>173084; 218433</t>
+          <t>173156; 218900</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>148610; 192795</t>
+          <t>146023; 190846</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>51391; 88319</t>
+          <t>59241; 98484</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>157496; 200591</t>
+          <t>158212; 199108</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>213919; 257928</t>
+          <t>211814; 257669</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>200332; 247330</t>
+          <t>199886; 247392</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>61398; 87154</t>
+          <t>70131; 101473</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>314220; 376466</t>
+          <t>313757; 375414</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>396623; 463409</t>
+          <t>396194; 466770</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>356025; 425595</t>
+          <t>358090; 423185</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>119173; 165568</t>
+          <t>138898; 190800</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>412231</t>
+          <t>478007</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>792702</t>
+          <t>673085</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1204933</t>
+          <t>1151093</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>902370; 1007998</t>
+          <t>907289; 1008885</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1471706; 1590298</t>
+          <t>1472550; 1593706</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1000723; 1113981</t>
+          <t>1004427; 1112384</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>313974; 463942</t>
+          <t>433346; 524533</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1112673; 1224850</t>
+          <t>1109829; 1221313</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1766895; 1889323</t>
+          <t>1772792; 1896297</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1311616; 1435478</t>
+          <t>1314759; 1437795</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>607145; 1318773</t>
+          <t>631731; 717387</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2052399; 2205057</t>
+          <t>2046214; 2200666</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3272612; 3446041</t>
+          <t>3277571; 3449689</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2346461; 2509717</t>
+          <t>2356845; 2510519</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>996081; 1806787</t>
+          <t>1091798; 1209072</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2C_R2-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P2C_R2-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados y estos son no remunerados (tasa de respuesta: 100,0%)</t>
+          <t>Población que convive con al menos un miembro que requiere cuidados y estos son no remunerados (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados y estos son no remunerados (tasa de respuesta: 100,0%)</t>
+          <t>Población que convive con al menos un miembro que requiere cuidados y estos son no remunerados (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
